--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5077351, 100797036</t>
+          <t xml:space="preserve">315128, 315129, 315130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>325</v>
+        <v>3456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735123, 5144023</t>
+          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>705</v>
+        <v>1775</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">735124, 4347931</t>
+          <t xml:space="preserve">315563</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F4">
-        <v>3000</v>
+        <v>264</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">735131, 5142874</t>
+          <t xml:space="preserve">315575, 315576</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>415</v>
+        <v>2655</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9761698</t>
+          <t xml:space="preserve">315575, 315578</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F6">
-        <v>5440</v>
+        <v>653</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,30 +331,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">315952, 315953, 315954</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>1170</v>
+        <v>2824</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034119</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142648</t>
+          <t xml:space="preserve">321325, 321326, 321327</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,21 +390,21 @@
         </is>
       </c>
       <c r="F8">
-        <v>767</v>
+        <v>3813</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058964</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-18</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142648</t>
+          <t xml:space="preserve">321345</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -440,21 +440,21 @@
         </is>
       </c>
       <c r="F9">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058964</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-18</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -481,35 +481,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">735111, 4358383</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>424</v>
+        <v>690</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376125</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -531,35 +531,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091449</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F11">
-        <v>1949</v>
+        <v>690</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311380467</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-03</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -581,35 +581,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F12">
-        <v>1811</v>
+        <v>690</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597643</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-04</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138663</t>
+          <t xml:space="preserve">321347, 321348, 321350</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -640,26 +640,26 @@
         </is>
       </c>
       <c r="F13">
-        <v>360</v>
+        <v>6736</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612418</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-01</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10125671</t>
+          <t xml:space="preserve">5077351, 100797036</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F14">
-        <v>374</v>
+        <v>325</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622674</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -731,35 +731,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144094</t>
+          <t xml:space="preserve">735124, 4347931</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>523</v>
+        <v>3000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622731</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -781,35 +781,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">735131, 5142874</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>13031</v>
+        <v>415</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622983</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,26 +840,26 @@
         </is>
       </c>
       <c r="F17">
-        <v>3592</v>
+        <v>1170</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">200034119</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -881,35 +881,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5142648</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">200058964</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -931,35 +931,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5142648</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>1200</v>
+        <v>592</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">200058964</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -981,35 +981,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">735123, 5144023</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
-        <v>11890</v>
+        <v>705</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624675</t>
+          <t xml:space="preserve">200059041</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2022-04-21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1031,25 +1031,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142428</t>
+          <t xml:space="preserve">735111, 4358383</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F21">
-        <v>6962</v>
+        <v>424</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624665</t>
+          <t xml:space="preserve">311376125</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2029-05-10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">100091449</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="F22">
-        <v>3488</v>
+        <v>1949</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632318</t>
+          <t xml:space="preserve">311380467</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2029-06-03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5138663</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>709</v>
+        <v>360</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632299</t>
+          <t xml:space="preserve">311612418</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-07-01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">10125671</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="F24">
-        <v>3414</v>
+        <v>374</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632278</t>
+          <t xml:space="preserve">311622674</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5144094</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F25">
-        <v>306</v>
+        <v>523</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632288</t>
+          <t xml:space="preserve">311622731</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>345</v>
+        <v>13031</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632285</t>
+          <t xml:space="preserve">311622983</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,25 +1331,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F27">
-        <v>1536</v>
+        <v>3592</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632306</t>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28">
-        <v>1592</v>
+        <v>782</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F29">
-        <v>929</v>
+        <v>1200</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>681</v>
+        <v>11890</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311624675</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144271</t>
+          <t xml:space="preserve">5142428</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="F31">
-        <v>8226</v>
+        <v>6962</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638729</t>
+          <t xml:space="preserve">311624665</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">321347, 321348, 321350</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="F32">
-        <v>6736</v>
+        <v>3488</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639923</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-02</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5143076</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F33">
-        <v>328</v>
+        <v>709</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646998</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-05</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142923</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>511</v>
+        <v>3414</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647593</t>
+          <t xml:space="preserve">311632278</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000541</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>1547</v>
+        <v>306</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649283</t>
+          <t xml:space="preserve">311632288</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-14</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138751</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F36">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650121</t>
+          <t xml:space="preserve">311632285</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289340</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F37">
-        <v>550</v>
+        <v>1536</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650123</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136092</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="F38">
-        <v>486</v>
+        <v>1592</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650984</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100066951</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>361</v>
+        <v>929</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652147</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-03</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139666</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F40">
-        <v>585</v>
+        <v>681</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652537</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870009</t>
+          <t xml:space="preserve">5144271</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="F41">
-        <v>715</v>
+        <v>8226</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652985</t>
+          <t xml:space="preserve">311638702</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140427</t>
+          <t xml:space="preserve">5143076</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="F42">
-        <v>482</v>
+        <v>328</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653312</t>
+          <t xml:space="preserve">311646998</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-10</t>
+          <t xml:space="preserve">2032-12-05</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140770</t>
+          <t xml:space="preserve">5142923</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,16 +2140,16 @@
         </is>
       </c>
       <c r="F43">
-        <v>654</v>
+        <v>511</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653561</t>
+          <t xml:space="preserve">311647593</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-11</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796007</t>
+          <t xml:space="preserve">7000541</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="F44">
-        <v>268</v>
+        <v>1547</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653615</t>
+          <t xml:space="preserve">311649283</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2032-12-14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8362229</t>
+          <t xml:space="preserve">5138751</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>5803</v>
+        <v>371</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655183</t>
+          <t xml:space="preserve">311650121</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7565490</t>
+          <t xml:space="preserve">8289340</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>2036</v>
+        <v>550</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656709</t>
+          <t xml:space="preserve">311650123</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5145779</t>
+          <t xml:space="preserve">5136092</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="F47">
-        <v>1546</v>
+        <v>486</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311650984</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5145779</t>
+          <t xml:space="preserve">100066951</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>4252</v>
+        <v>361</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311652147</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">5139666</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659784</t>
+          <t xml:space="preserve">311652537</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-13</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140009</t>
+          <t xml:space="preserve">7870009</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>1474</v>
+        <v>715</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665113</t>
+          <t xml:space="preserve">311652985</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138720</t>
+          <t xml:space="preserve">5140427</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="F51">
-        <v>1186</v>
+        <v>482</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667938</t>
+          <t xml:space="preserve">311653312</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138720</t>
+          <t xml:space="preserve">5140770</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>529</v>
+        <v>654</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667938</t>
+          <t xml:space="preserve">311653561</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-01-11</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">7796007</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>449</v>
+        <v>268</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667996</t>
+          <t xml:space="preserve">311653615</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">8362229</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>1036</v>
+        <v>5803</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668340</t>
+          <t xml:space="preserve">311655183</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">321345</t>
+          <t xml:space="preserve">7565490</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>679</v>
+        <v>2036</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671681</t>
+          <t xml:space="preserve">311656709</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">5145779</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>690</v>
+        <v>1546</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671684</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">5145779</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57">
-        <v>690</v>
+        <v>4252</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671684</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
-        <v>690</v>
+        <v>566</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671684</t>
+          <t xml:space="preserve">311659784</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951035</t>
+          <t xml:space="preserve">5140009</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>529</v>
+        <v>1474</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671706</t>
+          <t xml:space="preserve">311665113</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139665</t>
+          <t xml:space="preserve">5138720</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="F60">
-        <v>408</v>
+        <v>1186</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673253</t>
+          <t xml:space="preserve">311667938</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7653714</t>
+          <t xml:space="preserve">5138720</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>638</v>
+        <v>529</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675169</t>
+          <t xml:space="preserve">311667938</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9723509</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F62">
-        <v>751</v>
+        <v>449</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676118</t>
+          <t xml:space="preserve">311667996</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136614</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F63">
-        <v>3395</v>
+        <v>1036</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677651</t>
+          <t xml:space="preserve">311668340</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">9761698</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F64">
-        <v>3334</v>
+        <v>5440</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678659</t>
+          <t xml:space="preserve">311670678</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-04</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">7951035</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>2235</v>
+        <v>529</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678661</t>
+          <t xml:space="preserve">311671706</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-04</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493949</t>
+          <t xml:space="preserve">5139665</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>1140</v>
+        <v>408</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679342</t>
+          <t xml:space="preserve">311673253</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140426</t>
+          <t xml:space="preserve">7653714</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F67">
-        <v>2001</v>
+        <v>638</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679640</t>
+          <t xml:space="preserve">311675169</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">315128, 315129, 315130</t>
+          <t xml:space="preserve">9723509</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="F68">
-        <v>3456</v>
+        <v>751</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684239</t>
+          <t xml:space="preserve">311676118</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315576</t>
+          <t xml:space="preserve">5136614</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>2655</v>
+        <v>3395</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684376</t>
+          <t xml:space="preserve">311677651</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315578</t>
+          <t xml:space="preserve">1493949</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>653</v>
+        <v>1140</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684378</t>
+          <t xml:space="preserve">311679342</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
+          <t xml:space="preserve">5140426</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F71">
-        <v>1775</v>
+        <v>2001</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686186</t>
+          <t xml:space="preserve">311679640</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">315563</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>264</v>
+        <v>3334</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686187</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">315952, 315953, 315954</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F73">
-        <v>2824</v>
+        <v>2235</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686146</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">321325, 321326, 321327</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F74">
-        <v>3813</v>
+        <v>1811</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686196</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">

--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:L82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fynsgade 39</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">315128, 315129, 315130</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>3456</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">315561, 315562, 315563, 315564</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1775</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">315563</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>264</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 102</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">315575, 315576</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>2655</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 100A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">315575, 315578</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>653</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Degnelodden 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6623</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">315952, 315953, 315954</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>2824</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rahbæksvej 18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">321325, 321326, 321327</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>3813</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">321345</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>679</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">321346</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>690</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">321346</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>690</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">321346</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>690</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">321347, 321348, 321350</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>6736</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Teglgaardsvej 7</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5077351, 100797036</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>325</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blåhøjvej 10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">735124, 4347931</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>3000</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 30</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">735131, 5142874</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>415</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fælledvej 3B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140421</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1170</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">200034119</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingparken 60</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142648</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>767</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">200058964</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingparken 62</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142648</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>592</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">200058964</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egebjerg Landevej 82</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">735123, 5144023</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>705</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">200059041</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2022-04-21</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovvej 12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">735111, 4358383</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>424</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311376125</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-05-10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndervold 350</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">100091449</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1949</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311380467</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-06-03</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tårnvej 30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138663</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>360</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311612418</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-01</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvegade 9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">10125671</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>374</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311622674</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Billundvej 7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">5144094</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>523</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311622731</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311622997</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærvej 503</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136097</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>13031</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311622983</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærvej 501</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136097</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>3592</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311623383</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærvej 501</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136097</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>782</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311623383</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærvej 501</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136097</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>1200</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311623383</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fælledvej 3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140421</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>11890</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311624675</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jorden Rundt 1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142428</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>6962</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311624665</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>3488</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311632292</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 9</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>709</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311632292</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 9</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>3414</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311632278</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311632292</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 7</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>306</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311632288</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311632292</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 9</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>345</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311632285</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311632292</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 9</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142535</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1536</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311632292</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tårnvej 135</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138708</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1592</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311633484</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tårnvej 135A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138708</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>929</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311633484</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tårnvej 135B</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138708</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>681</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311633484</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakkevej 9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7250</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">5144271</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>8226</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311638702</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 167</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">5143076</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>328</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311646998</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-05</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142923</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>511</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311647593</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterbrogade 5C</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">7000541</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1547</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311649283</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-14</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borgergade 38</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138751</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>371</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311650121</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trehøjevej 18</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">8289340</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>550</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311650123</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærvej 124</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136092</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>486</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311650984</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Granvej 5A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">100066951</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>361</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311652147</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rolighedsvej 8</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">5139666</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>585</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311652537</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tuen 2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">7870009</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>715</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311652985</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 122</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140427</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>482</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311653312</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 25A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140770</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>654</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311653561</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-11</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndre Boulevard 13</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">7796007</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>268</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311653615</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirke Alle 7</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">8362229</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>5803</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311655183</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engdraget 8</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">7565490</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>2036</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311656709</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 9</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6623</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">5145779</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>1546</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311659176</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 9</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6623</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">5145779</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>4252</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311659176</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drivvejen 3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6623</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5146067</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>566</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311659784</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nymarksvej 10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140009</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>1474</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311665113</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Banegårdsvej 26</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138720</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>1186</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311667938</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Banegårdsvej 24A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5138720</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>529</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311667938</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fælledvej 3A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140421</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>449</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311667996</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestermarksvej 2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140421</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1036</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311668340</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løvlundvej 4B</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">9761698</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>5440</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311670678</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydtoften 8</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">7951035</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>529</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311671706</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 12A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">5139665</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>408</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311673253</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Morsbølvej 101</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">7653714</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>638</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311675169</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 12A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">9723509</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>751</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311676118</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hans Jensensvej 6</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">5136614</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>3395</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311677651</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvejen 385A</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">1493949</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>1140</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311679342</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langelandsvej 70</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">5140426</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>2001</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311679640</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 15F</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142582</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>3334</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311680381</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 15A</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142582</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>2235</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311680381</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 15C</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142582</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>1811</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311680381</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 16</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142495</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1991</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311686199</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tinghusgade 12</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">5142495</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>2526</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311686205</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drivvejen 1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6623</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5146067</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>6667</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311686166</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Teglgaardsvej 7</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">735144, 5077351</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>1538</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311686096</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Buen 6</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">9084190</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>607</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311686103</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Buen 6</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">9084190</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>1457</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311686103</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterbrogade 1A</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7200</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">9658844</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>519</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311735594</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-01-28</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,39 +4891,49 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovvej 15</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">9084136</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>1099</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311771547</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-04</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:L82"/>
 </worksheet>
 </file>
--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 39</t>
+          <t xml:space="preserve">Blåhøjvej 10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,7 +101,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315128, 315129, 315130</t>
+          <t xml:space="preserve">735124, 4347931</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>3456</v>
+        <v>3000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8A</t>
+          <t xml:space="preserve">Sydtoften 30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
+          <t xml:space="preserve">735131, 5142874</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>1775</v>
+        <v>415</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8B</t>
+          <t xml:space="preserve">Teglgaardsvej 7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">315563</t>
+          <t xml:space="preserve">5077351, 100797036</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H4">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 102</t>
+          <t xml:space="preserve">Fælledvej 3B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,30 +281,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315576</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H5">
-        <v>2655</v>
+        <v>1170</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200034119</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 100A</t>
+          <t xml:space="preserve">Tingparken 60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,30 +341,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315578</t>
+          <t xml:space="preserve">5142648</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>653</v>
+        <v>767</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200058964</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -391,40 +391,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnelodden 3</t>
+          <t xml:space="preserve">Tingparken 62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">315952, 315953, 315954</t>
+          <t xml:space="preserve">5142648</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>2824</v>
+        <v>592</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200058964</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -451,40 +451,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbæksvej 18</t>
+          <t xml:space="preserve">Egebjerg Landevej 82</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321325, 321326, 321327</t>
+          <t xml:space="preserve">735123, 5144023</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H8">
-        <v>3813</v>
+        <v>705</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200059041</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-04-21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -511,45 +511,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 1</t>
+          <t xml:space="preserve">Skovvej 12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">321345</t>
+          <t xml:space="preserve">735111, 4358383</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>679</v>
+        <v>424</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311376125</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-05-10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 3</t>
+          <t xml:space="preserve">Søndervold 350</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">100091449</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -590,26 +590,26 @@
         </is>
       </c>
       <c r="H10">
-        <v>690</v>
+        <v>1949</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311380467</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-06-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -631,45 +631,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 13</t>
+          <t xml:space="preserve">Tårnvej 30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">5138663</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>690</v>
+        <v>360</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311612418</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-07-01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -691,45 +691,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 23</t>
+          <t xml:space="preserve">Billundvej 7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">321346</t>
+          <t xml:space="preserve">5144094</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H12">
-        <v>690</v>
+        <v>523</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311622731</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -751,45 +751,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Torvegade 9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">321347, 321348, 321350</t>
+          <t xml:space="preserve">10125671</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>6736</v>
+        <v>374</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311622674</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -811,45 +811,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgaardsvej 7</t>
+          <t xml:space="preserve">Kærvej 503</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5077351, 100797036</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>325</v>
+        <v>13031</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311622983</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -871,45 +871,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blåhøjvej 10</t>
+          <t xml:space="preserve">Kærvej 501</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">735124, 4347931</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15">
-        <v>3000</v>
+        <v>3592</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -931,45 +931,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 30</t>
+          <t xml:space="preserve">Kærvej 501</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">735131, 5142874</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H16">
-        <v>415</v>
+        <v>782</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -991,45 +991,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3B</t>
+          <t xml:space="preserve">Kærvej 501</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">5136097</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H17">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034119</t>
+          <t xml:space="preserve">311623383</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingparken 60</t>
+          <t xml:space="preserve">Fælledvej 3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142648</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,26 +1070,26 @@
         </is>
       </c>
       <c r="H18">
-        <v>767</v>
+        <v>11890</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058964</t>
+          <t xml:space="preserve">311624675</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-18</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingparken 62</t>
+          <t xml:space="preserve">Jorden Rundt 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,35 +1121,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142648</t>
+          <t xml:space="preserve">5142428</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>592</v>
+        <v>6962</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058964</t>
+          <t xml:space="preserve">311624665</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-18</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1171,45 +1171,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egebjerg Landevej 82</t>
+          <t xml:space="preserve">Tinghusgade 7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">735123, 5144023</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H20">
-        <v>705</v>
+        <v>306</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059041</t>
+          <t xml:space="preserve">311632288</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-21</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1231,35 +1231,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 12</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">735111, 4358383</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>424</v>
+        <v>3488</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376125</t>
+          <t xml:space="preserve">311632318</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-10</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndervold 350</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,25 +1301,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091449</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H22">
-        <v>1949</v>
+        <v>709</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311380467</t>
+          <t xml:space="preserve">311632299</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-03</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 30</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,25 +1361,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138663</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>360</v>
+        <v>3414</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612418</t>
+          <t xml:space="preserve">311632278</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-01</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 9</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">10125671</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H24">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622674</t>
+          <t xml:space="preserve">311632285</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,35 +1471,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billundvej 7</t>
+          <t xml:space="preserve">Tinghusgade 9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144094</t>
+          <t xml:space="preserve">5142535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H25">
-        <v>523</v>
+        <v>1536</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622997</t>
+          <t xml:space="preserve">311632306</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 503</t>
+          <t xml:space="preserve">Tårnvej 135</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="H26">
-        <v>13031</v>
+        <v>1592</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622983</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 501</t>
+          <t xml:space="preserve">Tårnvej 135A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="H27">
-        <v>3592</v>
+        <v>929</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 501</t>
+          <t xml:space="preserve">Tårnvej 135B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5138708</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H28">
-        <v>782</v>
+        <v>681</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">311633484</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,35 +1711,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 501</t>
+          <t xml:space="preserve">Bakkevej 9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136097</t>
+          <t xml:space="preserve">5144271</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>1200</v>
+        <v>8226</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623383</t>
+          <t xml:space="preserve">311638729</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">321347, 321348, 321350</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>11890</v>
+        <v>6736</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624675</t>
+          <t xml:space="preserve">311639923</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2032-11-02</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jorden Rundt 1</t>
+          <t xml:space="preserve">Sydtoften 167</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142428</t>
+          <t xml:space="preserve">5143076</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="H31">
-        <v>6962</v>
+        <v>328</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624665</t>
+          <t xml:space="preserve">311646998</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2032-12-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Sydtoften 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5142923</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,16 +1910,16 @@
         </is>
       </c>
       <c r="H32">
-        <v>3488</v>
+        <v>511</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311647593</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Vesterbrogade 5C</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,25 +1961,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">7000541</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>709</v>
+        <v>1547</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311649283</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-12-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Borgergade 38</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,25 +2021,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5138751</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>3414</v>
+        <v>371</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311650121</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 7</t>
+          <t xml:space="preserve">Trehøjevej 18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">8289340</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>306</v>
+        <v>550</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311650123</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Kærvej 124</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">5136092</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>345</v>
+        <v>486</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311650984</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 9</t>
+          <t xml:space="preserve">Granvej 5A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142535</t>
+          <t xml:space="preserve">100066951</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>1536</v>
+        <v>361</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311652147</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-30</t>
+          <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135</t>
+          <t xml:space="preserve">Rolighedsvej 8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5139666</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="H38">
-        <v>1592</v>
+        <v>585</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311652537</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135A</t>
+          <t xml:space="preserve">Tuen 2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">7870009</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>929</v>
+        <v>715</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311652985</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 135B</t>
+          <t xml:space="preserve">Vestergade 122</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138708</t>
+          <t xml:space="preserve">5140427</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>681</v>
+        <v>482</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633484</t>
+          <t xml:space="preserve">311653312</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-05</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 9</t>
+          <t xml:space="preserve">Østergade 25A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5144271</t>
+          <t xml:space="preserve">5140770</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,16 +2450,16 @@
         </is>
       </c>
       <c r="H41">
-        <v>8226</v>
+        <v>654</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638702</t>
+          <t xml:space="preserve">311653561</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2033-01-11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 167</t>
+          <t xml:space="preserve">Søndre Boulevard 13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5143076</t>
+          <t xml:space="preserve">7796007</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,16 +2510,16 @@
         </is>
       </c>
       <c r="H42">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646998</t>
+          <t xml:space="preserve">311653615</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-05</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 4</t>
+          <t xml:space="preserve">Kirke Alle 7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142923</t>
+          <t xml:space="preserve">8362229</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H43">
-        <v>511</v>
+        <v>5803</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647593</t>
+          <t xml:space="preserve">311655183</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbrogade 5C</t>
+          <t xml:space="preserve">Engdraget 8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000541</t>
+          <t xml:space="preserve">7565490</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="H44">
-        <v>1547</v>
+        <v>2036</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649283</t>
+          <t xml:space="preserve">311656709</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-14</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 38</t>
+          <t xml:space="preserve">Stadionvej 9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138751</t>
+          <t xml:space="preserve">5145779</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="H45">
-        <v>371</v>
+        <v>1546</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650121</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trehøjevej 18</t>
+          <t xml:space="preserve">Stadionvej 9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289340</t>
+          <t xml:space="preserve">5145779</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H46">
-        <v>550</v>
+        <v>4252</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650123</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-19</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,35 +2791,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 124</t>
+          <t xml:space="preserve">Drivvejen 3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136092</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H47">
-        <v>486</v>
+        <v>566</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650984</t>
+          <t xml:space="preserve">311659784</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granvej 5A</t>
+          <t xml:space="preserve">Nymarksvej 10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100066951</t>
+          <t xml:space="preserve">5140009</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="H48">
-        <v>361</v>
+        <v>1474</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652147</t>
+          <t xml:space="preserve">311665113</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-03</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 8</t>
+          <t xml:space="preserve">Banegårdsvej 24A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,25 +2921,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139666</t>
+          <t xml:space="preserve">5138720</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H49">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652537</t>
+          <t xml:space="preserve">311667938</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuen 2</t>
+          <t xml:space="preserve">Banegårdsvej 26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7870009</t>
+          <t xml:space="preserve">5138720</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>715</v>
+        <v>1186</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652985</t>
+          <t xml:space="preserve">311667938</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 122</t>
+          <t xml:space="preserve">Fælledvej 3A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140427</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H51">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653312</t>
+          <t xml:space="preserve">311667996</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-10</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 25A</t>
+          <t xml:space="preserve">Vestermarksvej 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140770</t>
+          <t xml:space="preserve">5140421</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H52">
-        <v>654</v>
+        <v>1036</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653561</t>
+          <t xml:space="preserve">311668340</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-11</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,35 +3151,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Boulevard 13</t>
+          <t xml:space="preserve">Løvlundvej 4B</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796007</t>
+          <t xml:space="preserve">9761698</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H53">
-        <v>268</v>
+        <v>5440</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653615</t>
+          <t xml:space="preserve">311670678</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Alle 7</t>
+          <t xml:space="preserve">Lindevej 1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8362229</t>
+          <t xml:space="preserve">321345</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>5803</v>
+        <v>679</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655183</t>
+          <t xml:space="preserve">311671681</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 8</t>
+          <t xml:space="preserve">Lindevej 13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7565490</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H55">
-        <v>2036</v>
+        <v>690</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656709</t>
+          <t xml:space="preserve">311671684</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9</t>
+          <t xml:space="preserve">Lindevej 23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5145779</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H56">
-        <v>1546</v>
+        <v>690</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311671684</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,35 +3391,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9</t>
+          <t xml:space="preserve">Lindevej 3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5145779</t>
+          <t xml:space="preserve">321346</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>4252</v>
+        <v>690</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311671684</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,35 +3451,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 3</t>
+          <t xml:space="preserve">Sydtoften 8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">7951035</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659784</t>
+          <t xml:space="preserve">311671706</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-13</t>
+          <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymarksvej 10</t>
+          <t xml:space="preserve">Engvej 12A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140009</t>
+          <t xml:space="preserve">5139665</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>1474</v>
+        <v>408</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665113</t>
+          <t xml:space="preserve">311673253</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsvej 26</t>
+          <t xml:space="preserve">Morsbølvej 101</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138720</t>
+          <t xml:space="preserve">7653714</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H60">
-        <v>1186</v>
+        <v>638</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667938</t>
+          <t xml:space="preserve">311675169</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsvej 24A</t>
+          <t xml:space="preserve">Skolevej 12A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5138720</t>
+          <t xml:space="preserve">9723509</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>529</v>
+        <v>751</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667938</t>
+          <t xml:space="preserve">311676118</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælledvej 3A</t>
+          <t xml:space="preserve">Hans Jensensvej 6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">5136614</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>449</v>
+        <v>3395</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667996</t>
+          <t xml:space="preserve">311677651</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarksvej 2</t>
+          <t xml:space="preserve">Langelandsvej 70</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140421</t>
+          <t xml:space="preserve">5140426</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H63">
-        <v>1036</v>
+        <v>2001</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668340</t>
+          <t xml:space="preserve">311679640</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvlundvej 4B</t>
+          <t xml:space="preserve">Tingvejen 385A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9761698</t>
+          <t xml:space="preserve">1493949</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>5440</v>
+        <v>1140</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670678</t>
+          <t xml:space="preserve">311679342</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 8</t>
+          <t xml:space="preserve">Tinghusgade 15A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951035</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H65">
-        <v>529</v>
+        <v>2235</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671706</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-04</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 12A</t>
+          <t xml:space="preserve">Tinghusgade 15C</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5139665</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H66">
-        <v>408</v>
+        <v>1811</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673253</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsbølvej 101</t>
+          <t xml:space="preserve">Tinghusgade 15F</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7653714</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>638</v>
+        <v>3334</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675169</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-21</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12A</t>
+          <t xml:space="preserve">Fynsgade 39</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9723509</t>
+          <t xml:space="preserve">315128, 315129, 315130</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>751</v>
+        <v>3456</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676118</t>
+          <t xml:space="preserve">311684239</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Jensensvej 6</t>
+          <t xml:space="preserve">Sydtoften 100A</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5136614</t>
+          <t xml:space="preserve">315575, 315578</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H69">
-        <v>3395</v>
+        <v>653</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677651</t>
+          <t xml:space="preserve">311684378</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-01</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 385A</t>
+          <t xml:space="preserve">Sydtoften 102</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493949</t>
+          <t xml:space="preserve">315575, 315576</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>1140</v>
+        <v>2655</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679342</t>
+          <t xml:space="preserve">311684376</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 70</t>
+          <t xml:space="preserve">Buen 6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,25 +4241,25 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140426</t>
+          <t xml:space="preserve">9084190</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>2001</v>
+        <v>607</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679640</t>
+          <t xml:space="preserve">311686103</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15F</t>
+          <t xml:space="preserve">Buen 6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,25 +4301,25 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">9084190</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H72">
-        <v>3334</v>
+        <v>1457</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311686103</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15A</t>
+          <t xml:space="preserve">Degnelodden 3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">315952, 315953, 315954</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>2235</v>
+        <v>2824</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311686146</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15C</t>
+          <t xml:space="preserve">Drivvejen 1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>1811</v>
+        <v>6667</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311686166</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 16</t>
+          <t xml:space="preserve">Kirkevej 8A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142495</t>
+          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>1991</v>
+        <v>1775</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686199</t>
+          <t xml:space="preserve">311686186</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 12</t>
+          <t xml:space="preserve">Kirkevej 8B</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142495</t>
+          <t xml:space="preserve">315563</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,11 +4550,11 @@
         </is>
       </c>
       <c r="H76">
-        <v>2526</v>
+        <v>264</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686205</t>
+          <t xml:space="preserve">311686187</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 1</t>
+          <t xml:space="preserve">Rahbæksvej 18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">321325, 321326, 321327</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="H77">
-        <v>6667</v>
+        <v>3813</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686166</t>
+          <t xml:space="preserve">311686196</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 6</t>
+          <t xml:space="preserve">Tinghusgade 12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,20 +4721,20 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084190</t>
+          <t xml:space="preserve">5142495</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H79">
-        <v>607</v>
+        <v>2526</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686103</t>
+          <t xml:space="preserve">311686205</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 6</t>
+          <t xml:space="preserve">Tinghusgade 16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084190</t>
+          <t xml:space="preserve">5142495</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>1457</v>
+        <v>1991</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686103</t>
+          <t xml:space="preserve">311686199</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">

--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622731</t>
+          <t xml:space="preserve">311622997</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632318</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632278</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632285</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638729</t>
+          <t xml:space="preserve">311638702</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">

--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:M82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -299,15 +319,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -359,15 +384,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S (Kolding)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -419,15 +449,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S (Kolding)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-04-18</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve">JA-Byggerådgivning</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-04-21</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">PAARUP arkitekter</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-10</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-03</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-01</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1194,20 +1289,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632288</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1314,20 +1419,25 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632299</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1494,20 +1614,25 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632306</t>
+          <t xml:space="preserve">311632292</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-30</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-05</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Factum2 A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-02</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-05</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-14</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-19</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-11</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2694,20 +2914,25 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311659209</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2754,20 +2979,25 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659176</t>
+          <t xml:space="preserve">311659209</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-13</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-04</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-21</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-01</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-28</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,21 +5324,26 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">STD Klima og Byggeri</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-04</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
+  <autoFilter ref="A1:M82"/>
 </worksheet>
 </file>
--- a/public/exports/29189765.xlsx
+++ b/public/exports/29189765.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622997</t>
+          <t xml:space="preserve">311622731</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311632288</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311632278</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632292</t>
+          <t xml:space="preserve">311632285</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659209</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659209</t>
+          <t xml:space="preserve">311659176</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
